--- a/scripts/fixtures/Заявка-тест-CRM.xlsx
+++ b/scripts/fixtures/Заявка-тест-CRM.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E6"/>
+  <dimension ref="B2:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -468,7 +468,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>7730303346</t>
+          <t>7703822568</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46037</v>
+        <v>45679</v>
       </c>
       <c r="E4" t="n">
-        <v>150000</v>
+        <v>314752</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>7707487208</t>
+          <t>7743622734</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -495,16 +495,16 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46063</v>
+        <v>45685</v>
       </c>
       <c r="E5" t="n">
-        <v>220500</v>
+        <v>186420</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>9731112323</t>
+          <t>7713151911</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -513,10 +513,46 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46086</v>
+        <v>45693</v>
       </c>
       <c r="E6" t="n">
-        <v>98500</v>
+        <v>92500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7720313708</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5507266215</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45700</v>
+      </c>
+      <c r="E7" t="n">
+        <v>203150</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7730303346</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5507266215</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45708</v>
+      </c>
+      <c r="E8" t="n">
+        <v>150000</v>
       </c>
     </row>
   </sheetData>
